--- a/exports/TCS_full_report.xlsx
+++ b/exports/TCS_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q82"/>
+  <dimension ref="A1:U82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>3.56</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44580.55208333334</v>
+        <v>44581.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>3919.5</v>
+        <v>3841.5</v>
       </c>
       <c r="I2" t="n">
         <v>3868.882056942146</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K2" t="n">
-        <v>0.84</v>
+        <v>-1.17</v>
       </c>
       <c r="L2" t="n">
         <v>1.29</v>
@@ -555,7 +578,7 @@
         <v>0.72</v>
       </c>
       <c r="N2" t="n">
-        <v>1.86</v>
+        <v>2.2</v>
       </c>
       <c r="O2" t="n">
         <v>0.65</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>5.1</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44593.55208333334</v>
+        <v>44594.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>3805</v>
+        <v>3855</v>
       </c>
       <c r="I3" t="n">
         <v>3837.355475335237</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K3" t="n">
-        <v>0.95</v>
+        <v>-0.35</v>
       </c>
       <c r="L3" t="n">
         <v>2.03</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>5.16</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44603.38541666666</v>
+        <v>44603.55208333334</v>
       </c>
       <c r="H4" t="n">
-        <v>3712.2</v>
+        <v>3693</v>
       </c>
       <c r="I4" t="n">
         <v>3699.277332182195</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>9</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="K4" t="n">
-        <v>-3.7</v>
+        <v>-4.2</v>
       </c>
       <c r="L4" t="n">
         <v>4.28</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>3.81</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44607.38541666666</v>
+        <v>44607.55208333334</v>
       </c>
       <c r="H5" t="n">
-        <v>3780.7</v>
+        <v>3834.55</v>
       </c>
       <c r="I5" t="n">
         <v>3833.677153519966</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>3.833333333333333</v>
+        <v>4</v>
       </c>
       <c r="K5" t="n">
-        <v>-2.37</v>
+        <v>-3.83</v>
       </c>
       <c r="L5" t="n">
-        <v>2.84</v>
+        <v>3.83</v>
       </c>
       <c r="M5" t="n">
         <v>1.53</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -762,28 +833,28 @@
         <v>4.61</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44613.55208333334</v>
+        <v>44614.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>3718.95</v>
+        <v>3580.7</v>
       </c>
       <c r="I6" t="n">
         <v>3680.865016617995</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>6</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K6" t="n">
-        <v>-3.01</v>
+        <v>-6.62</v>
       </c>
       <c r="L6" t="n">
-        <v>3.36</v>
+        <v>6.82</v>
       </c>
       <c r="M6" t="n">
-        <v>0.39</v>
+        <v>1.85</v>
       </c>
       <c r="N6" t="n">
-        <v>2.11</v>
+        <v>3.44</v>
       </c>
       <c r="O6" t="n">
         <v>2.83</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>6.12</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44628.55208333334</v>
+        <v>44629.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>3594</v>
+        <v>3648.75</v>
       </c>
       <c r="I7" t="n">
         <v>3610.227732876046</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.37</v>
+        <v>-1.9</v>
       </c>
       <c r="L7" t="n">
         <v>2.33</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>5.8</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44658.38541666666</v>
+        <v>44658.55208333334</v>
       </c>
       <c r="H8" t="n">
-        <v>3718</v>
+        <v>3682.95</v>
       </c>
       <c r="I8" t="n">
         <v>3704.712627238676</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>29</v>
+        <v>29.16666666666667</v>
       </c>
       <c r="K8" t="n">
-        <v>1.9</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L8" t="n">
         <v>1.88</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>3.71</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44671.55208333334</v>
+        <v>44672.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>3558</v>
+        <v>3636.95</v>
       </c>
       <c r="I9" t="n">
         <v>3633.816731437416</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>13</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K9" t="n">
-        <v>3.39</v>
+        <v>1.25</v>
       </c>
       <c r="L9" t="n">
         <v>1.52</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,28 +1109,28 @@
         <v>5.71</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44686.55208333334</v>
+        <v>44687.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>3508.75</v>
+        <v>3459.1</v>
       </c>
       <c r="I10" t="n">
         <v>3463.443137503911</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K10" t="n">
-        <v>-3.52</v>
+        <v>-4.89</v>
       </c>
       <c r="L10" t="n">
-        <v>4.72</v>
+        <v>5.8</v>
       </c>
       <c r="M10" t="n">
         <v>1.52</v>
       </c>
       <c r="N10" t="n">
-        <v>1.84</v>
+        <v>1.93</v>
       </c>
       <c r="O10" t="n">
         <v>1.77</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>4.17</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44708.55208333334</v>
+        <v>44711.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>3266.7</v>
+        <v>3379</v>
       </c>
       <c r="I11" t="n">
         <v>3335.304718393078</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K11" t="n">
-        <v>5.56</v>
+        <v>2.32</v>
       </c>
       <c r="L11" t="n">
         <v>1.04</v>
@@ -1068,7 +1199,7 @@
         <v>1.19</v>
       </c>
       <c r="N11" t="n">
-        <v>2.42</v>
+        <v>3.47</v>
       </c>
       <c r="O11" t="n">
         <v>-1.93</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,28 +1247,28 @@
         <v>6.22</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44722.55208333334</v>
+        <v>44725.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>3357.75</v>
+        <v>3222.35</v>
       </c>
       <c r="I12" t="n">
         <v>3317.85396902149</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.63</v>
+        <v>-4.64</v>
       </c>
       <c r="L12" t="n">
-        <v>2.72</v>
+        <v>4.64</v>
       </c>
       <c r="M12" t="n">
-        <v>1.54</v>
+        <v>2.02</v>
       </c>
       <c r="N12" t="n">
-        <v>2.25</v>
+        <v>3.95</v>
       </c>
       <c r="O12" t="n">
         <v>3.47</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,28 +1316,28 @@
         <v>6.37</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44734.55208333334</v>
+        <v>44735.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>3225</v>
+        <v>3270.1</v>
       </c>
       <c r="I13" t="n">
         <v>3239.839602786861</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.08</v>
+        <v>-1.48</v>
       </c>
       <c r="L13" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="M13" t="n">
         <v>1.09</v>
       </c>
       <c r="N13" t="n">
-        <v>2.55</v>
+        <v>2.73</v>
       </c>
       <c r="O13" t="n">
         <v>-3.95</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1218,28 +1385,28 @@
         <v>5.7</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44750.55208333334</v>
+        <v>44753.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>3266.5</v>
+        <v>3122</v>
       </c>
       <c r="I14" t="n">
         <v>3170.3895815148</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.11</v>
+        <v>-4.53</v>
       </c>
       <c r="L14" t="n">
-        <v>2.07</v>
+        <v>5.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1.42</v>
+        <v>1.85</v>
       </c>
       <c r="N14" t="n">
-        <v>2.89</v>
+        <v>4.73</v>
       </c>
       <c r="O14" t="n">
         <v>2.73</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,28 +1454,28 @@
         <v>6.86</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44761.55208333334</v>
+        <v>44762.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>3074</v>
+        <v>3153</v>
       </c>
       <c r="I15" t="n">
         <v>3129.116634840286</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K15" t="n">
-        <v>1.54</v>
+        <v>-0.99</v>
       </c>
       <c r="L15" t="n">
         <v>3.28</v>
       </c>
       <c r="M15" t="n">
-        <v>0.93</v>
+        <v>1.1</v>
       </c>
       <c r="N15" t="n">
-        <v>2.37</v>
+        <v>2.8</v>
       </c>
       <c r="O15" t="n">
         <v>-4.73</v>
@@ -1305,7 +1484,19 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S15" t="b">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1332,28 +1523,28 @@
         <v>5.44</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44795.55208333334</v>
+        <v>44796.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>3354</v>
+        <v>3293.8</v>
       </c>
       <c r="I16" t="n">
         <v>3308.425495627991</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>33.16666666666666</v>
+        <v>34</v>
       </c>
       <c r="K16" t="n">
-        <v>6.37</v>
+        <v>4.47</v>
       </c>
       <c r="L16" t="n">
         <v>1.79</v>
       </c>
       <c r="M16" t="n">
-        <v>0.65</v>
+        <v>1.02</v>
       </c>
       <c r="N16" t="n">
-        <v>1.48</v>
+        <v>1.58</v>
       </c>
       <c r="O16" t="n">
         <v>2.8</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>3.6</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44813.55208333334</v>
+        <v>44816.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>3221</v>
+        <v>3252</v>
       </c>
       <c r="I17" t="n">
         <v>3234.67300798755</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K17" t="n">
-        <v>2.21</v>
+        <v>1.27</v>
       </c>
       <c r="L17" t="n">
         <v>1.44</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,28 +1661,28 @@
         <v>3.37</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44817.55208333334</v>
+        <v>44818.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>3233.5</v>
+        <v>3127.05</v>
       </c>
       <c r="I18" t="n">
         <v>3142.56322554088</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>2</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.57</v>
+        <v>-3.84</v>
       </c>
       <c r="L18" t="n">
-        <v>0.83</v>
+        <v>4.21</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N18" t="n">
-        <v>0.14</v>
+        <v>3.36</v>
       </c>
       <c r="O18" t="n">
         <v>0.53</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>3.94</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>44838.38541666666</v>
+        <v>44838.55208333334</v>
       </c>
       <c r="H19" t="n">
-        <v>3078</v>
+        <v>3095</v>
       </c>
       <c r="I19" t="n">
         <v>3093.919543216893</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>20</v>
+        <v>20.16666666666667</v>
       </c>
       <c r="K19" t="n">
-        <v>1.57</v>
+        <v>1.02</v>
       </c>
       <c r="L19" t="n">
         <v>0.46</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>4.7</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>44902.55208333334</v>
+        <v>44903.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>3370</v>
+        <v>3352.1</v>
       </c>
       <c r="I20" t="n">
         <v>3356.539477938823</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>64</v>
+        <v>64.83333333333333</v>
       </c>
       <c r="K20" t="n">
-        <v>8.890000000000001</v>
+        <v>8.31</v>
       </c>
       <c r="L20" t="n">
         <v>2.75</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>86</v>
+        <v>87</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>3.28</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>44936.55208333334</v>
+        <v>44937.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>3283</v>
+        <v>3341.25</v>
       </c>
       <c r="I21" t="n">
         <v>3313.330335558822</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>33.16666666666666</v>
+        <v>34</v>
       </c>
       <c r="K21" t="n">
-        <v>2.06</v>
+        <v>0.32</v>
       </c>
       <c r="L21" t="n">
         <v>0.74</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>5.33</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>44978.55208333334</v>
+        <v>44979.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>3452</v>
+        <v>3416.1</v>
       </c>
       <c r="I22" t="n">
         <v>3450.456243921459</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>41.16666666666666</v>
+        <v>42</v>
       </c>
       <c r="K22" t="n">
-        <v>3.31</v>
+        <v>2.24</v>
       </c>
       <c r="L22" t="n">
         <v>2.09</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>3.49</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45019.55208333334</v>
+        <v>45021.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>3202</v>
+        <v>3249.55</v>
       </c>
       <c r="I23" t="n">
         <v>3227.829921212916</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>40.16666666666666</v>
+        <v>42</v>
       </c>
       <c r="K23" t="n">
-        <v>6.27</v>
+        <v>4.88</v>
       </c>
       <c r="L23" t="n">
         <v>1.06</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1788,25 +2075,25 @@
         <v>4.67</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45029.55208333334</v>
+        <v>45033.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>3192</v>
+        <v>3128</v>
       </c>
       <c r="I24" t="n">
         <v>3148.345004073895</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.77</v>
+        <v>-3.74</v>
       </c>
       <c r="L24" t="n">
-        <v>2.14</v>
+        <v>5.52</v>
       </c>
       <c r="M24" t="n">
-        <v>1.09</v>
+        <v>1.81</v>
       </c>
       <c r="N24" t="n">
         <v>1.72</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>4.17</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45043.55208333334</v>
+        <v>45044.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>3189.9</v>
+        <v>3219.9</v>
       </c>
       <c r="I25" t="n">
         <v>3210.025665399942</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.98</v>
+        <v>-2.94</v>
       </c>
       <c r="L25" t="n">
-        <v>2.56</v>
+        <v>3.17</v>
       </c>
       <c r="M25" t="n">
         <v>0.51</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>3.2</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45062.55208333334</v>
+        <v>45063.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>3256</v>
+        <v>3203.4</v>
       </c>
       <c r="I26" t="n">
         <v>3207.144041964927</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K26" t="n">
-        <v>1.12</v>
+        <v>-0.51</v>
       </c>
       <c r="L26" t="n">
         <v>1.45</v>
@@ -1923,7 +2234,7 @@
         <v>0.06</v>
       </c>
       <c r="N26" t="n">
-        <v>1.15</v>
+        <v>1.44</v>
       </c>
       <c r="O26" t="n">
         <v>0.79</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>4.34</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45068.38541666666</v>
+        <v>45068.55208333334</v>
       </c>
       <c r="H27" t="n">
-        <v>3263.7</v>
+        <v>3292</v>
       </c>
       <c r="I27" t="n">
         <v>3290.176173058009</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>5</v>
+        <v>5.166666666666667</v>
       </c>
       <c r="K27" t="n">
-        <v>-1.88</v>
+        <v>-2.77</v>
       </c>
       <c r="L27" t="n">
-        <v>2.39</v>
+        <v>3.27</v>
       </c>
       <c r="M27" t="n">
         <v>0.53</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2016,28 +2351,28 @@
         <v>3.29</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45082.55208333334</v>
+        <v>45083.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>3289.3</v>
+        <v>3224.8</v>
       </c>
       <c r="I28" t="n">
         <v>3238.837534077808</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>14</v>
+        <v>14.83333333333333</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.08</v>
+        <v>-2.04</v>
       </c>
       <c r="L28" t="n">
-        <v>0.97</v>
+        <v>2.16</v>
       </c>
       <c r="M28" t="n">
         <v>0.58</v>
       </c>
       <c r="N28" t="n">
-        <v>0.88</v>
+        <v>1.59</v>
       </c>
       <c r="O28" t="n">
         <v>2.09</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>3.99</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45105.55208333334</v>
+        <v>45107.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>3222.85</v>
+        <v>3290.5</v>
       </c>
       <c r="I29" t="n">
         <v>3258.518485682106</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K29" t="n">
-        <v>0.06</v>
+        <v>-2.04</v>
       </c>
       <c r="L29" t="n">
-        <v>1.86</v>
+        <v>2.08</v>
       </c>
       <c r="M29" t="n">
         <v>0.62</v>
       </c>
       <c r="N29" t="n">
-        <v>1.2</v>
+        <v>2.34</v>
       </c>
       <c r="O29" t="n">
         <v>-1.59</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>3.97</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45134.55208333334</v>
+        <v>45135.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>3397.95</v>
+        <v>3355.8</v>
       </c>
       <c r="I30" t="n">
         <v>3361.077959824738</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K30" t="n">
-        <v>3.27</v>
+        <v>1.98</v>
       </c>
       <c r="L30" t="n">
         <v>2.32</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,25 +2558,25 @@
         <v>3.48</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45142.55208333334</v>
+        <v>45145.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>3441.05</v>
+        <v>3478</v>
       </c>
       <c r="I31" t="n">
         <v>3455.658407590652</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>10</v>
       </c>
       <c r="K31" t="n">
-        <v>-2.54</v>
+        <v>-3.64</v>
       </c>
       <c r="L31" t="n">
-        <v>3.43</v>
+        <v>3.66</v>
       </c>
       <c r="M31" t="n">
-        <v>0.31</v>
+        <v>0.37</v>
       </c>
       <c r="N31" t="n">
         <v>1.85</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2244,28 +2627,28 @@
         <v>3.76</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45155.55208333334</v>
+        <v>45156.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>3425.9</v>
+        <v>3364.45</v>
       </c>
       <c r="I32" t="n">
         <v>3374.399501606317</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K32" t="n">
-        <v>-1.5</v>
+        <v>-3.26</v>
       </c>
       <c r="L32" t="n">
-        <v>1.93</v>
+        <v>3.31</v>
       </c>
       <c r="M32" t="n">
         <v>0.49</v>
       </c>
       <c r="N32" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.69</v>
       </c>
       <c r="O32" t="n">
         <v>1.22</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>3.77</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45176.38541666666</v>
+        <v>45176.55208333334</v>
       </c>
       <c r="H33" t="n">
-        <v>3441.6</v>
+        <v>3459</v>
       </c>
       <c r="I33" t="n">
         <v>3448.353027549985</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>20</v>
+        <v>20.16666666666667</v>
       </c>
       <c r="K33" t="n">
-        <v>-2.29</v>
+        <v>-2.81</v>
       </c>
       <c r="L33" t="n">
-        <v>2.51</v>
+        <v>2.84</v>
       </c>
       <c r="M33" t="n">
         <v>0.68</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>2.9</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45202.38541666666</v>
+        <v>45202.55208333334</v>
       </c>
       <c r="H34" t="n">
-        <v>3524.95</v>
+        <v>3507.1</v>
       </c>
       <c r="I34" t="n">
         <v>3513.329970337419</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>25.83333333333333</v>
+        <v>26</v>
       </c>
       <c r="K34" t="n">
-        <v>1.91</v>
+        <v>1.39</v>
       </c>
       <c r="L34" t="n">
         <v>0.6899999999999999</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>3.84</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45205.38541666666</v>
+        <v>45205.55208333334</v>
       </c>
       <c r="H35" t="n">
-        <v>3601.3</v>
+        <v>3621.25</v>
       </c>
       <c r="I35" t="n">
         <v>3613.04482517108</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>2.833333333333333</v>
+        <v>3</v>
       </c>
       <c r="K35" t="n">
-        <v>-2.69</v>
+        <v>-3.25</v>
       </c>
       <c r="L35" t="n">
-        <v>3.33</v>
+        <v>3.65</v>
       </c>
       <c r="M35" t="n">
         <v>0.25</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,22 +2903,22 @@
         <v>3.77</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45216.38541666666</v>
+        <v>45216.55208333334</v>
       </c>
       <c r="H36" t="n">
-        <v>3520.2</v>
+        <v>3508.1</v>
       </c>
       <c r="I36" t="n">
         <v>3519.453636516256</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>10.83333333333333</v>
+        <v>11</v>
       </c>
       <c r="K36" t="n">
-        <v>-2.79</v>
+        <v>-3.12</v>
       </c>
       <c r="L36" t="n">
-        <v>3.04</v>
+        <v>3.26</v>
       </c>
       <c r="M36" t="n">
         <v>1.05</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>2.94</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45245.38541666666</v>
+        <v>45245.55208333334</v>
       </c>
       <c r="H37" t="n">
-        <v>3392.75</v>
+        <v>3408.6</v>
       </c>
       <c r="I37" t="n">
         <v>3407.184914373481</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>28.83333333333333</v>
+        <v>29</v>
       </c>
       <c r="K37" t="n">
-        <v>3.29</v>
+        <v>2.84</v>
       </c>
       <c r="L37" t="n">
         <v>0.42</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>2.68</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45294.55208333334</v>
+        <v>45295.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>3692.6</v>
+        <v>3665.45</v>
       </c>
       <c r="I38" t="n">
         <v>3686.58710027272</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>49</v>
+        <v>49.83333333333334</v>
       </c>
       <c r="K38" t="n">
-        <v>8.33</v>
+        <v>7.54</v>
       </c>
       <c r="L38" t="n">
         <v>0.51</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -2643,28 +3110,28 @@
         <v>4.31</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45302.55208333334</v>
+        <v>45303.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>3726.7</v>
+        <v>3896.9</v>
       </c>
       <c r="I39" t="n">
         <v>3798.557223605041</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K39" t="n">
-        <v>-1.67</v>
+        <v>-6.31</v>
       </c>
       <c r="L39" t="n">
-        <v>2.93</v>
+        <v>6.54</v>
       </c>
       <c r="M39" t="n">
-        <v>0.79</v>
+        <v>3.25</v>
       </c>
       <c r="N39" t="n">
-        <v>1.92</v>
+        <v>4.16</v>
       </c>
       <c r="O39" t="n">
         <v>-0.67</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,22 +3179,22 @@
         <v>5.23</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45315.55208333334</v>
+        <v>45316.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>3859.4</v>
+        <v>3795.75</v>
       </c>
       <c r="I40" t="n">
         <v>3805.044968365545</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.96</v>
+        <v>-2.6</v>
       </c>
       <c r="L40" t="n">
-        <v>2.34</v>
+        <v>3.03</v>
       </c>
       <c r="M40" t="n">
         <v>1.07</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>4.76</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45324.38541666666</v>
+        <v>45324.55208333334</v>
       </c>
       <c r="H41" t="n">
-        <v>3945</v>
+        <v>3959.2</v>
       </c>
       <c r="I41" t="n">
         <v>3947.493876114872</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K41" t="n">
-        <v>-3.93</v>
+        <v>-4.31</v>
       </c>
       <c r="L41" t="n">
         <v>4.97</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,28 +3317,28 @@
         <v>4.32</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45369.55208333334</v>
+        <v>45370.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>4144.25</v>
+        <v>4014.55</v>
       </c>
       <c r="I42" t="n">
         <v>4047.627279621541</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>45</v>
+        <v>45.83333333333334</v>
       </c>
       <c r="K42" t="n">
-        <v>4.67</v>
+        <v>1.4</v>
       </c>
       <c r="L42" t="n">
         <v>0.37</v>
       </c>
       <c r="M42" t="n">
-        <v>0.92</v>
+        <v>2.24</v>
       </c>
       <c r="N42" t="n">
-        <v>1.84</v>
+        <v>4.18</v>
       </c>
       <c r="O42" t="n">
         <v>3.03</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>5.8</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45419.38541666666</v>
+        <v>45419.55208333334</v>
       </c>
       <c r="H43" t="n">
-        <v>3930</v>
+        <v>3975.2</v>
       </c>
       <c r="I43" t="n">
         <v>3960.837953122983</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>49</v>
+        <v>49.16666666666666</v>
       </c>
       <c r="K43" t="n">
-        <v>2.11</v>
+        <v>0.98</v>
       </c>
       <c r="L43" t="n">
         <v>1.24</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>3</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2928,25 +3455,25 @@
         <v>4.2</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45430.38541666666</v>
+        <v>45433.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>3853.35</v>
+        <v>3817.9</v>
       </c>
       <c r="I44" t="n">
         <v>3820.498881532923</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>10.83333333333333</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K44" t="n">
-        <v>-3.07</v>
+        <v>-3.96</v>
       </c>
       <c r="L44" t="n">
-        <v>3.65</v>
+        <v>4.15</v>
       </c>
       <c r="M44" t="n">
-        <v>0.36</v>
+        <v>0.59</v>
       </c>
       <c r="N44" t="n">
         <v>1.54</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>3.82</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45449.38541666666</v>
+        <v>45449.55208333334</v>
       </c>
       <c r="H45" t="n">
-        <v>3795.75</v>
+        <v>3836</v>
       </c>
       <c r="I45" t="n">
         <v>3807.259715546447</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>16</v>
+        <v>16.16666666666667</v>
       </c>
       <c r="K45" t="n">
-        <v>0.58</v>
+        <v>-0.47</v>
       </c>
       <c r="L45" t="n">
         <v>2.37</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>4.69</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45506.55208333334</v>
+        <v>45509.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>4283.85</v>
+        <v>4143.4</v>
       </c>
       <c r="I46" t="n">
         <v>4242.511831482134</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>57</v>
+        <v>59.83333333333334</v>
       </c>
       <c r="K46" t="n">
-        <v>11.67</v>
+        <v>8.01</v>
       </c>
       <c r="L46" t="n">
         <v>1.46</v>
       </c>
       <c r="M46" t="n">
-        <v>0.58</v>
+        <v>1.05</v>
       </c>
       <c r="N46" t="n">
-        <v>2.35</v>
+        <v>2.89</v>
       </c>
       <c r="O46" t="n">
         <v>2.15</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>3</v>
+      </c>
+      <c r="U46" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -3099,28 +3662,28 @@
         <v>5.48</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45518.55208333334</v>
+        <v>45520.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>4293</v>
+        <v>4400.45</v>
       </c>
       <c r="I47" t="n">
         <v>4346.932137450422</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>11</v>
       </c>
       <c r="K47" t="n">
-        <v>-3.61</v>
+        <v>-6.2</v>
       </c>
       <c r="L47" t="n">
-        <v>3.93</v>
+        <v>6.42</v>
       </c>
       <c r="M47" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="N47" t="n">
-        <v>2.29</v>
+        <v>2.82</v>
       </c>
       <c r="O47" t="n">
         <v>-2.89</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>4.91</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45552.55208333334</v>
+        <v>45553.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>4511</v>
+        <v>4343.1</v>
       </c>
       <c r="I48" t="n">
         <v>4395.922870124252</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>32.16666666666666</v>
+        <v>33</v>
       </c>
       <c r="K48" t="n">
-        <v>2.51</v>
+        <v>-1.3</v>
       </c>
       <c r="L48" t="n">
         <v>1.71</v>
@@ -3177,7 +3752,7 @@
         <v>1.17</v>
       </c>
       <c r="N48" t="n">
-        <v>0.95</v>
+        <v>3.62</v>
       </c>
       <c r="O48" t="n">
         <v>2.82</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>6.03</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45601.55208333334</v>
+        <v>45602.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>3971.45</v>
+        <v>4122.55</v>
       </c>
       <c r="I49" t="n">
         <v>4098.010357454052</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>48.16666666666666</v>
+        <v>49</v>
       </c>
       <c r="K49" t="n">
-        <v>8.56</v>
+        <v>5.08</v>
       </c>
       <c r="L49" t="n">
         <v>3.54</v>
@@ -3234,7 +3821,7 @@
         <v>0.97</v>
       </c>
       <c r="N49" t="n">
-        <v>1.12</v>
+        <v>4.32</v>
       </c>
       <c r="O49" t="n">
         <v>-3.62</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>3</v>
+      </c>
+      <c r="U49" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>5.84</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45610.55208333334</v>
+        <v>45614.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>4148</v>
+        <v>4021</v>
       </c>
       <c r="I50" t="n">
         <v>4030.728112821931</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K50" t="n">
-        <v>0.62</v>
+        <v>-2.46</v>
       </c>
       <c r="L50" t="n">
         <v>3.57</v>
@@ -3291,7 +3890,7 @@
         <v>0.4</v>
       </c>
       <c r="N50" t="n">
-        <v>0.68</v>
+        <v>3.15</v>
       </c>
       <c r="O50" t="n">
         <v>4.32</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>6.97</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45618.38541666666</v>
+        <v>45618.55208333334</v>
       </c>
       <c r="H51" t="n">
-        <v>4160</v>
+        <v>4221.95</v>
       </c>
       <c r="I51" t="n">
         <v>4210.547145920228</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>4</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="K51" t="n">
-        <v>-3.46</v>
+        <v>-5</v>
       </c>
       <c r="L51" t="n">
-        <v>4.77</v>
+        <v>5.82</v>
       </c>
       <c r="M51" t="n">
         <v>1.57</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3384,25 +4007,25 @@
         <v>5.72</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45644.55208333334</v>
+        <v>45645.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>4355.65</v>
+        <v>4284.6</v>
       </c>
       <c r="I52" t="n">
         <v>4315.906995765497</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>26</v>
+        <v>26.83333333333333</v>
       </c>
       <c r="K52" t="n">
-        <v>3.17</v>
+        <v>1.48</v>
       </c>
       <c r="L52" t="n">
         <v>1.58</v>
       </c>
       <c r="M52" t="n">
-        <v>0.72</v>
+        <v>1.69</v>
       </c>
       <c r="N52" t="n">
         <v>2.11</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>4.78</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45666.55208333334</v>
+        <v>45667.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>4044</v>
+        <v>4278</v>
       </c>
       <c r="I53" t="n">
         <v>4200.065399613266</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K53" t="n">
-        <v>5.62</v>
+        <v>0.15</v>
       </c>
       <c r="L53" t="n">
         <v>2.27</v>
       </c>
       <c r="M53" t="n">
-        <v>1.12</v>
+        <v>3.86</v>
       </c>
       <c r="N53" t="n">
-        <v>1.59</v>
+        <v>5.51</v>
       </c>
       <c r="O53" t="n">
         <v>-1.71</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,22 +4145,22 @@
         <v>6.61</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45674.55208333334</v>
+        <v>45677.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>4130</v>
+        <v>4077.45</v>
       </c>
       <c r="I54" t="n">
         <v>4083.053540650214</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>10</v>
       </c>
       <c r="K54" t="n">
-        <v>-3.46</v>
+        <v>-4.69</v>
       </c>
       <c r="L54" t="n">
-        <v>4.16</v>
+        <v>4.84</v>
       </c>
       <c r="M54" t="n">
         <v>1.31</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>5.53</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45737.55208333334</v>
+        <v>45740.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>3578</v>
+        <v>3639.3</v>
       </c>
       <c r="I55" t="n">
         <v>3613.190743814167</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>60.16666666666666</v>
+        <v>63</v>
       </c>
       <c r="K55" t="n">
-        <v>12.25</v>
+        <v>10.75</v>
       </c>
       <c r="L55" t="n">
         <v>2.79</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>88</v>
+        <v>89</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>3</v>
+      </c>
+      <c r="U55" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -3612,28 +4283,28 @@
         <v>5.52</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45748.55208333334</v>
+        <v>45750.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>3555.95</v>
+        <v>3405.45</v>
       </c>
       <c r="I56" t="n">
         <v>3510.527044515609</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K56" t="n">
-        <v>-2.29</v>
+        <v>-6.43</v>
       </c>
       <c r="L56" t="n">
-        <v>3.14</v>
+        <v>6.68</v>
       </c>
       <c r="M56" t="n">
-        <v>0.87</v>
+        <v>1.83</v>
       </c>
       <c r="N56" t="n">
-        <v>1.33</v>
+        <v>4.29</v>
       </c>
       <c r="O56" t="n">
         <v>1.54</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>6.46</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45764.55208333334</v>
+        <v>45768.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>3297.4</v>
+        <v>3349.1</v>
       </c>
       <c r="I57" t="n">
         <v>3347.874238426792</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K57" t="n">
-        <v>3.17</v>
+        <v>1.65</v>
       </c>
       <c r="L57" t="n">
         <v>2.84</v>
@@ -3699,7 +4382,19 @@
         <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S57" t="b">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>6.21</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45807.38541666666</v>
+        <v>45807.55208333334</v>
       </c>
       <c r="H58" t="n">
-        <v>3490</v>
+        <v>3460</v>
       </c>
       <c r="I58" t="n">
         <v>3463.135925853408</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>39</v>
+        <v>39.16666666666666</v>
       </c>
       <c r="K58" t="n">
-        <v>4.21</v>
+        <v>3.31</v>
       </c>
       <c r="L58" t="n">
         <v>1.94</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>3</v>
+      </c>
+      <c r="U58" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>3.3</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45818.55208333334</v>
+        <v>45819.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>3461.9</v>
+        <v>3484.4</v>
       </c>
       <c r="I59" t="n">
         <v>3466.560338449355</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>11</v>
+        <v>11.83333333333333</v>
       </c>
       <c r="K59" t="n">
-        <v>-0.05</v>
+        <v>-0.71</v>
       </c>
       <c r="L59" t="n">
         <v>0.92</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S59" t="b">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3840,22 +4559,22 @@
         <v>3.16</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45828.55208333334</v>
+        <v>45831.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>3429.1</v>
+        <v>3389.7</v>
       </c>
       <c r="I60" t="n">
         <v>3418.300993740501</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K60" t="n">
-        <v>-1.59</v>
+        <v>-2.72</v>
       </c>
       <c r="L60" t="n">
-        <v>2.62</v>
+        <v>3.28</v>
       </c>
       <c r="M60" t="n">
         <v>1.13</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>3.35</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45888.55208333334</v>
+        <v>45889.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>3018</v>
+        <v>3089</v>
       </c>
       <c r="I61" t="n">
         <v>3084.486169717174</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>57.16666666666666</v>
+        <v>58</v>
       </c>
       <c r="K61" t="n">
-        <v>10.97</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="L61" t="n">
         <v>2.96</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>3</v>
+      </c>
+      <c r="U61" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>3.98</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45904.55208333334</v>
+        <v>45905.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>3095.8</v>
+        <v>3039.2</v>
       </c>
       <c r="I62" t="n">
         <v>3055.440187816137</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K62" t="n">
-        <v>0.22</v>
+        <v>-1.61</v>
       </c>
       <c r="L62" t="n">
         <v>2.53</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,25 +4766,25 @@
         <v>4.38</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45910.55208333334</v>
+        <v>45911.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>3110</v>
+        <v>3121.6</v>
       </c>
       <c r="I63" t="n">
         <v>3121.034040887757</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K63" t="n">
-        <v>-2.33</v>
+        <v>-2.71</v>
       </c>
       <c r="L63" t="n">
-        <v>2.75</v>
+        <v>3.28</v>
       </c>
       <c r="M63" t="n">
-        <v>0.3</v>
+        <v>0.93</v>
       </c>
       <c r="N63" t="n">
         <v>1.9</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S63" t="b">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -4068,28 +4835,28 @@
         <v>3</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45919.55208333334</v>
+        <v>45922.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>3171</v>
+        <v>3075.5</v>
       </c>
       <c r="I64" t="n">
         <v>3100.767750597706</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>11</v>
       </c>
       <c r="K64" t="n">
-        <v>1.58</v>
+        <v>-1.48</v>
       </c>
       <c r="L64" t="n">
-        <v>0.82</v>
+        <v>1.81</v>
       </c>
       <c r="M64" t="n">
-        <v>0.22</v>
+        <v>2.4</v>
       </c>
       <c r="N64" t="n">
-        <v>0.66</v>
+        <v>3.01</v>
       </c>
       <c r="O64" t="n">
         <v>0.49</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S64" t="b">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>3.8</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45936.38541666666</v>
+        <v>45936.55208333334</v>
       </c>
       <c r="H65" t="n">
-        <v>2969.5</v>
+        <v>2988</v>
       </c>
       <c r="I65" t="n">
         <v>2976.032011976693</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>14</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="K65" t="n">
-        <v>3.45</v>
+        <v>2.85</v>
       </c>
       <c r="L65" t="n">
         <v>1.02</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>3.56</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45964.55208333334</v>
+        <v>45965.38541666666</v>
       </c>
       <c r="H66" t="n">
-        <v>3019.5</v>
+        <v>2983</v>
       </c>
       <c r="I66" t="n">
         <v>2988.238304262937</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>28</v>
+        <v>28.83333333333333</v>
       </c>
       <c r="K66" t="n">
-        <v>1.05</v>
+        <v>-0.17</v>
       </c>
       <c r="L66" t="n">
         <v>1.5</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,28 +5042,28 @@
         <v>3.78</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>45972.55208333334</v>
+        <v>45973.38541666666</v>
       </c>
       <c r="H67" t="n">
-        <v>3049</v>
+        <v>3125</v>
       </c>
       <c r="I67" t="n">
         <v>3071.916790833297</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K67" t="n">
-        <v>-2.21</v>
+        <v>-4.76</v>
       </c>
       <c r="L67" t="n">
-        <v>2.44</v>
+        <v>4.79</v>
       </c>
       <c r="M67" t="n">
         <v>0.66</v>
       </c>
       <c r="N67" t="n">
-        <v>1.05</v>
+        <v>2.51</v>
       </c>
       <c r="O67" t="n">
         <v>-1.08</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S67" t="b">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>1</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>4.38</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46021.55208333334</v>
+        <v>46022.38541666666</v>
       </c>
       <c r="H68" t="n">
-        <v>3255</v>
+        <v>3221.7</v>
       </c>
       <c r="I68" t="n">
         <v>3233.543608358495</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>48.16666666666666</v>
+        <v>49</v>
       </c>
       <c r="K68" t="n">
-        <v>4.16</v>
+        <v>3.09</v>
       </c>
       <c r="L68" t="n">
         <v>2.17</v>
@@ -4317,7 +5132,7 @@
         <v>0.48</v>
       </c>
       <c r="N68" t="n">
-        <v>1.09</v>
+        <v>1.38</v>
       </c>
       <c r="O68" t="n">
         <v>2.51</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>3</v>
+      </c>
+      <c r="U68" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="69">
@@ -4353,25 +5180,25 @@
         <v>2.88</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46055.55208333334</v>
+        <v>46056.38541666666</v>
       </c>
       <c r="H69" t="n">
-        <v>3167</v>
+        <v>3228.4</v>
       </c>
       <c r="I69" t="n">
         <v>3223.786836605587</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>33.16666666666666</v>
+        <v>34</v>
       </c>
       <c r="K69" t="n">
-        <v>1.7</v>
+        <v>-0.21</v>
       </c>
       <c r="L69" t="n">
-        <v>2.45</v>
+        <v>3.98</v>
       </c>
       <c r="M69" t="n">
-        <v>1.21</v>
+        <v>5.78</v>
       </c>
       <c r="N69" t="n">
         <v>1.69</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4410,28 +5249,28 @@
         <v>4.33</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46056.55208333334</v>
+        <v>46057.38541666666</v>
       </c>
       <c r="H70" t="n">
-        <v>3220</v>
+        <v>3001.8</v>
       </c>
       <c r="I70" t="n">
         <v>3088.738955425892</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>1</v>
       </c>
       <c r="K70" t="n">
-        <v>-0.26</v>
+        <v>-7.02</v>
       </c>
       <c r="L70" t="n">
-        <v>1.3</v>
+        <v>7.51</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>6.84</v>
       </c>
       <c r="O70" t="n">
         <v>1.67</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S70" t="b">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>1</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -4467,19 +5318,19 @@
         <v>9.01</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46118.55208333334</v>
+        <v>46119.38541666666</v>
       </c>
       <c r="H71" t="n">
-        <v>2474.8</v>
+        <v>2526.7</v>
       </c>
       <c r="I71" t="n">
         <v>2488.715241417609</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>61.16666666666666</v>
+        <v>62</v>
       </c>
       <c r="K71" t="n">
-        <v>17.56</v>
+        <v>15.83</v>
       </c>
       <c r="L71" t="n">
         <v>3.94</v>
@@ -4488,7 +5339,7 @@
         <v>2.71</v>
       </c>
       <c r="N71" t="n">
-        <v>1.95</v>
+        <v>2.69</v>
       </c>
       <c r="O71" t="n">
         <v>-6.84</v>
@@ -4497,7 +5348,19 @@
         <v>1</v>
       </c>
       <c r="Q71" t="n">
-        <v>80</v>
+        <v>81</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>3</v>
+      </c>
+      <c r="U71" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="72">
@@ -4524,28 +5387,28 @@
         <v>6.96</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46135.55208333334</v>
+        <v>46136.38541666666</v>
       </c>
       <c r="H72" t="n">
-        <v>2518.2</v>
+        <v>2395.8</v>
       </c>
       <c r="I72" t="n">
         <v>2504.669998288686</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K72" t="n">
-        <v>-0.34</v>
+        <v>-5.18</v>
       </c>
       <c r="L72" t="n">
-        <v>3.11</v>
+        <v>5.37</v>
       </c>
       <c r="M72" t="n">
         <v>1.31</v>
       </c>
       <c r="N72" t="n">
-        <v>2.86</v>
+        <v>4.65</v>
       </c>
       <c r="O72" t="n">
         <v>2.69</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S72" t="b">
+        <v>0</v>
+      </c>
+      <c r="T72" t="n">
+        <v>1</v>
+      </c>
+      <c r="U72" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -4581,19 +5456,19 @@
         <v>8.24</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46174.55208333334</v>
+        <v>46175.38541666666</v>
       </c>
       <c r="H73" t="n">
-        <v>2296.4</v>
+        <v>2444.7</v>
       </c>
       <c r="I73" t="n">
         <v>2354.979026569646</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>38.16666666666666</v>
+        <v>39</v>
       </c>
       <c r="K73" t="n">
-        <v>4.15</v>
+        <v>-2.04</v>
       </c>
       <c r="L73" t="n">
         <v>4.56</v>
@@ -4602,7 +5477,7 @@
         <v>1.24</v>
       </c>
       <c r="N73" t="n">
-        <v>1.96</v>
+        <v>6.74</v>
       </c>
       <c r="O73" t="n">
         <v>-4.65</v>
@@ -4611,7 +5486,19 @@
         <v>1</v>
       </c>
       <c r="Q73" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>3</v>
+      </c>
+      <c r="U73" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -4638,28 +5525,28 @@
         <v>8.58</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46175.55208333334</v>
+        <v>46176.38541666666</v>
       </c>
       <c r="H74" t="n">
-        <v>2451.1</v>
+        <v>2239.3</v>
       </c>
       <c r="I74" t="n">
         <v>2303.389664255757</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>1</v>
       </c>
       <c r="K74" t="n">
-        <v>0.26</v>
+        <v>-8.4</v>
       </c>
       <c r="L74" t="n">
-        <v>5.26</v>
+        <v>8.99</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>8.41</v>
       </c>
       <c r="O74" t="n">
         <v>6.74</v>
@@ -4668,7 +5555,19 @@
         <v>1</v>
       </c>
       <c r="Q74" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S74" t="b">
+        <v>0</v>
+      </c>
+      <c r="T74" t="n">
+        <v>1</v>
+      </c>
+      <c r="U74" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -4695,19 +5594,19 @@
         <v>11.85</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46213.55208333334</v>
+        <v>46216.38541666666</v>
       </c>
       <c r="H75" t="n">
-        <v>2067.9</v>
+        <v>2195.9</v>
       </c>
       <c r="I75" t="n">
         <v>2114.07353332113</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>37.16666666666666</v>
+        <v>40</v>
       </c>
       <c r="K75" t="n">
-        <v>7.65</v>
+        <v>1.94</v>
       </c>
       <c r="L75" t="n">
         <v>6.86</v>
@@ -4716,7 +5615,7 @@
         <v>2.24</v>
       </c>
       <c r="N75" t="n">
-        <v>4.49</v>
+        <v>5.56</v>
       </c>
       <c r="O75" t="n">
         <v>-8.41</v>
@@ -4725,7 +5624,19 @@
         <v>1</v>
       </c>
       <c r="Q75" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>2</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -4752,19 +5663,19 @@
         <v>9.32</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>46245.55208333334</v>
+        <v>46246.38541666666</v>
       </c>
       <c r="H76" t="n">
-        <v>2442.1</v>
+        <v>2325.2</v>
       </c>
       <c r="I76" t="n">
         <v>2337.808739749408</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K76" t="n">
-        <v>11.21</v>
+        <v>5.89</v>
       </c>
       <c r="L76" t="n">
         <v>5.96</v>
@@ -4773,7 +5684,7 @@
         <v>2.01</v>
       </c>
       <c r="N76" t="n">
-        <v>2.77</v>
+        <v>4.16</v>
       </c>
       <c r="O76" t="n">
         <v>5.56</v>
@@ -4782,7 +5693,19 @@
         <v>1</v>
       </c>
       <c r="Q76" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S76" t="b">
+        <v>1</v>
+      </c>
+      <c r="T76" t="n">
+        <v>2</v>
+      </c>
+      <c r="U76" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -4809,19 +5732,19 @@
         <v>8</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>46261.55208333334</v>
+        <v>46262.38541666666</v>
       </c>
       <c r="H77" t="n">
-        <v>2253.6</v>
+        <v>2343.7</v>
       </c>
       <c r="I77" t="n">
         <v>2341.057725354255</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K77" t="n">
-        <v>3.08</v>
+        <v>-0.8</v>
       </c>
       <c r="L77" t="n">
         <v>5.19</v>
@@ -4830,7 +5753,7 @@
         <v>1.42</v>
       </c>
       <c r="N77" t="n">
-        <v>1.14</v>
+        <v>3.92</v>
       </c>
       <c r="O77" t="n">
         <v>-4.16</v>
@@ -4839,7 +5762,19 @@
         <v>1</v>
       </c>
       <c r="Q77" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S77" t="b">
+        <v>1</v>
+      </c>
+      <c r="T77" t="n">
+        <v>2</v>
+      </c>
+      <c r="U77" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -4866,19 +5801,19 @@
         <v>6.11</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>46273.38541666666</v>
+        <v>46273.55208333334</v>
       </c>
       <c r="H78" t="n">
-        <v>2272</v>
+        <v>2262</v>
       </c>
       <c r="I78" t="n">
         <v>2265.054560730009</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>11</v>
+        <v>11.16666666666667</v>
       </c>
       <c r="K78" t="n">
-        <v>-3.06</v>
+        <v>-3.49</v>
       </c>
       <c r="L78" t="n">
         <v>4.25</v>
@@ -4896,7 +5831,19 @@
         <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S78" t="b">
+        <v>0</v>
+      </c>
+      <c r="T78" t="n">
+        <v>1</v>
+      </c>
+      <c r="U78" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -4923,28 +5870,28 @@
         <v>4.13</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>46276.55208333334</v>
+        <v>46280.38541666666</v>
       </c>
       <c r="H79" t="n">
-        <v>2207.9</v>
+        <v>2289.9</v>
       </c>
       <c r="I79" t="n">
         <v>2288.826461093256</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>3</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K79" t="n">
-        <v>2.39</v>
+        <v>-1.23</v>
       </c>
       <c r="L79" t="n">
-        <v>0.55</v>
+        <v>2.7</v>
       </c>
       <c r="M79" t="n">
-        <v>0.01</v>
+        <v>3.06</v>
       </c>
       <c r="N79" t="n">
-        <v>0.39</v>
+        <v>2.53</v>
       </c>
       <c r="O79" t="n">
         <v>-0.53</v>
@@ -4953,7 +5900,19 @@
         <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R79" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S79" t="b">
+        <v>0</v>
+      </c>
+      <c r="T79" t="n">
+        <v>1</v>
+      </c>
+      <c r="U79" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -4980,28 +5939,28 @@
         <v>4.74</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>46282.55208333334</v>
+        <v>46283.38541666666</v>
       </c>
       <c r="H80" t="n">
-        <v>2193.5</v>
+        <v>2114.9</v>
       </c>
       <c r="I80" t="n">
         <v>2181.371909863017</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>3</v>
       </c>
       <c r="K80" t="n">
-        <v>-4.21</v>
+        <v>-7.64</v>
       </c>
       <c r="L80" t="n">
-        <v>5.56</v>
+        <v>7.73</v>
       </c>
       <c r="M80" t="n">
-        <v>0.5</v>
+        <v>0.74</v>
       </c>
       <c r="N80" t="n">
-        <v>3.62</v>
+        <v>4.04</v>
       </c>
       <c r="O80" t="n">
         <v>2.53</v>
@@ -5010,7 +5969,19 @@
         <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R80" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S80" t="b">
+        <v>0</v>
+      </c>
+      <c r="T80" t="n">
+        <v>1</v>
+      </c>
+      <c r="U80" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -5037,28 +6008,28 @@
         <v>8.15</v>
       </c>
       <c r="G81" s="1" t="n">
-        <v>46303.55208333334</v>
+        <v>46304.38541666666</v>
       </c>
       <c r="H81" t="n">
-        <v>2077</v>
+        <v>2163</v>
       </c>
       <c r="I81" t="n">
         <v>2142.985212525379</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K81" t="n">
-        <v>1.79</v>
+        <v>-2.27</v>
       </c>
       <c r="L81" t="n">
-        <v>2.95</v>
+        <v>4.21</v>
       </c>
       <c r="M81" t="n">
         <v>1.84</v>
       </c>
       <c r="N81" t="n">
-        <v>1.4</v>
+        <v>4.55</v>
       </c>
       <c r="O81" t="n">
         <v>-4.04</v>
@@ -5067,7 +6038,19 @@
         <v>1</v>
       </c>
       <c r="Q81" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R81" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S81" t="b">
+        <v>1</v>
+      </c>
+      <c r="T81" t="n">
+        <v>2</v>
+      </c>
+      <c r="U81" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="82">
@@ -5118,6 +6101,14 @@
       <c r="Q82" t="n">
         <v>26</v>
       </c>
+      <c r="R82" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S82" t="b">
+        <v>1</v>
+      </c>
+      <c r="T82" t="inlineStr"/>
+      <c r="U82" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7220,7 +8211,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20.5</v>
+        <v>21.7</v>
       </c>
     </row>
     <row r="6">
@@ -7230,7 +8221,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14.2</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="7">
@@ -7240,7 +8231,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>64</v>
+        <v>64.8</v>
       </c>
     </row>
     <row r="8">
@@ -7250,7 +8241,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -7260,7 +8251,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>29</v>
+        <v>29.4</v>
       </c>
     </row>
     <row r="10">
@@ -7270,7 +8261,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>48.2</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11">
@@ -7310,7 +8301,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.56</v>
+        <v>-0.66</v>
       </c>
     </row>
     <row r="15">
@@ -7320,7 +8311,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.11</v>
+        <v>-1.29</v>
       </c>
     </row>
     <row r="16">
@@ -7330,7 +8321,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.01</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="17">
@@ -7340,7 +8331,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>17.56</v>
+        <v>15.83</v>
       </c>
     </row>
     <row r="18">
@@ -7350,7 +8341,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>57.5</v>
+        <v>36.2</v>
       </c>
     </row>
     <row r="19">
@@ -7360,7 +8351,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.54</v>
+        <v>3.28</v>
       </c>
     </row>
     <row r="20">
@@ -7370,7 +8361,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.38</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -7380,7 +8371,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>6.86</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="22">
@@ -7390,7 +8381,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23">
@@ -7410,7 +8401,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.98</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="25">
@@ -7420,7 +8411,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.71</v>
+        <v>5.78</v>
       </c>
     </row>
     <row r="26">
@@ -7430,7 +8421,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.91</v>
+        <v>2.81</v>
       </c>
     </row>
     <row r="27">
@@ -7440,7 +8431,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4.49</v>
+        <v>8.41</v>
       </c>
     </row>
     <row r="28">
@@ -7450,7 +8441,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29">
